--- a/human_resources_forms/049_hiring_bonus_requisition_addendum_form--human_resources_forms.xlsx
+++ b/human_resources_forms/049_hiring_bonus_requisition_addendum_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single',_'label':_'single',_'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Single', 'label': 'Single', 'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'quarterly',_'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Quarterly', 'label': 'Quarterly', 'value': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'semi-annual',_'label':_'semi-annual',_'value':_'semi-annual'}</t>
+          <t>semi-annual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Semi-Annual', 'label': 'Semi-Annual', 'value': 'Semi-Annual'}</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'annually',_'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Annually', 'label': 'Annually', 'value': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'at_hire',_'label':_'at_hire',_'value':_'at_hire'}</t>
+          <t>at_hire</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'At Hire', 'label': 'At Hire', 'value': 'At Hire'}</t>
+          <t>At Hire</t>
         </is>
       </c>
     </row>
